--- a/forms/trg/Formulir_TRG_swm-rg.xlsx
+++ b/forms/trg/Formulir_TRG_swm-rg.xlsx
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
